--- a/dcf/KLAC.xlsx
+++ b/dcf/KLAC.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.08903252026797463</v>
+        <v>0.08816413009209145</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.09403252026797464</v>
+        <v>0.09316413009209146</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.09903252026797463</v>
+        <v>0.09816413009209145</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.1040325202679746</v>
+        <v>0.1031641300920915</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1090325202679746</v>
+        <v>0.1081641300920915</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1140325202679746</v>
+        <v>0.1131641300920914</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1190325202679746</v>
+        <v>0.1181641300920915</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>935.4781499328724</v>
+        <v>839.1075043424161</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>901.37079036917</v>
+        <v>808.9440424277392</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>868.7960641354794</v>
+        <v>780.1298988505266</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>837.6761654638565</v>
+        <v>752.5966820392514</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>807.9376244428536</v>
+        <v>726.2798099028048</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>779.5110455072656</v>
+        <v>701.1182800562342</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>752.3308628474548</v>
+        <v>677.0544549174147</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>993.6764596525326</v>
+        <v>889.9587572868675</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>956.963333504935</v>
+        <v>857.5167137614238</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>921.9106041574372</v>
+        <v>826.5357963603266</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>888.4336624025855</v>
+        <v>796.9416551258084</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>856.4526256252004</v>
+        <v>768.664092045831</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>825.8920522317828</v>
+        <v>741.6368101757151</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>796.6806745799108</v>
+        <v>715.7971790179913</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1051.874769372193</v>
+        <v>940.8100102313189</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>1012.5558766407</v>
+        <v>906.0893850951085</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>975.0251441793952</v>
+        <v>872.9416938701264</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>939.1911593413145</v>
+        <v>841.2866282123654</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>904.9676268075473</v>
+        <v>811.0483741888573</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>872.2730589563001</v>
+        <v>782.155340295196</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>841.0304863123666</v>
+        <v>754.5399031185678</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1110.073079091853</v>
+        <v>991.6612631757702</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1068.148419776465</v>
+        <v>954.6620564287932</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>1028.139684201353</v>
+        <v>919.3475913799264</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>989.9486562800435</v>
+        <v>885.6316012989223</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>953.4826279898941</v>
+        <v>853.4326563318835</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>918.6540656808171</v>
+        <v>822.6738704146768</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>885.3802980448226</v>
+        <v>793.2826272191445</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1168.271388811513</v>
+        <v>1042.512516120222</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>1123.74096291223</v>
+        <v>1003.234727762478</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>1081.254224223311</v>
+        <v>965.7534888897264</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1040.706153218772</v>
+        <v>929.9765743854792</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>1001.997629172241</v>
+        <v>895.8169384749099</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>965.0350724053344</v>
+        <v>863.1924005341577</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>929.7301097772786</v>
+        <v>832.025351319721</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1226.469698531173</v>
+        <v>1093.363769064673</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1179.333506047995</v>
+        <v>1051.807399096162</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1134.368764245268</v>
+        <v>1012.159386399526</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1091.463650157501</v>
+        <v>974.3215474720364</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1050.512630354588</v>
+        <v>938.2012206179361</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>1011.416079129852</v>
+        <v>903.7109306536386</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>974.0799215097346</v>
+        <v>870.7680754202977</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1284.668008250833</v>
+        <v>1144.215022009124</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1234.926049183759</v>
+        <v>1100.380070429847</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>1187.483304267226</v>
+        <v>1058.565283909326</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>1142.22114709623</v>
+        <v>1018.666520558593</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1099.027631536935</v>
+        <v>980.5855027609624</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>1057.797085854369</v>
+        <v>944.2294607731194</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1018.42973324219</v>
+        <v>909.5107995208743</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>235.5500030517578</v>
+        <v>218.3099975585938</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.1040325202679746</v>
+        <v>0.1031641300920915</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.037502669433193</v>
+        <v>1.040982384781423</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>235.5500030517578</v>
+        <v>218.3099975585938</v>
       </c>
     </row>
     <row r="49">
@@ -24414,7 +24414,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>989.9486562800435</v>
+        <v>885.6316012989223</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>1322.813498582646</v>
+        <v>1154.804160362043</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>734.8682542943649</v>
+        <v>673.7312905669369</v>
       </c>
     </row>
     <row r="59">
